--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_chara.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_chara.xlsx
@@ -448,11 +448,6 @@
           <t>$sup</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>$sup</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="12.8" customHeight="1" s="7">
       <c r="D14" s="6" t="inlineStr">
@@ -521,9 +516,9 @@
           <t>(You talk to yourself)</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>(Você fala consigo mesmo)</t>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>(Você fala sozinho)</t>
         </is>
       </c>
     </row>
@@ -575,11 +570,6 @@
           <t>$sup</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>$sup</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="12.8" customHeight="1" s="7">
       <c r="D31" s="6" t="inlineStr">
@@ -624,11 +614,6 @@
           <t>$rumor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>$rumor</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="12.8" customHeight="1" s="7">
       <c r="B39" s="6" t="inlineStr">
@@ -659,7 +644,7 @@
           <t>Join us! (#2)</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>Junte-se a nós! (#2)</t>
         </is>
@@ -694,7 +679,7 @@
           <t>Join us! #1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>Junte-se a nós! #1</t>
         </is>
@@ -724,9 +709,9 @@
           <t>Please leave.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Mudei de ideia.</t>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Por favor, vá embora.</t>
         </is>
       </c>
     </row>
@@ -755,11 +740,6 @@
           <t>$hired</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>$contratado</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="12.8" customHeight="1" s="7">
       <c r="D46" s="6" t="inlineStr">
@@ -796,11 +776,6 @@
       <c r="J49" s="6" t="inlineStr">
         <is>
           <t>$hired</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>$contratada</t>
         </is>
       </c>
     </row>
@@ -870,9 +845,9 @@
           <t>I will call #1 now.</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Eu chamarei #1 agora.</t>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Vou chamar #1 agora.</t>
         </is>
       </c>
     </row>
@@ -916,7 +891,7 @@
           <t>(#self is asleep)</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="6" t="inlineStr">
         <is>
           <t>(#self está dormindo)</t>
         </is>
@@ -950,9 +925,9 @@
           <t>Save me!</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Me salve!</t>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>Me salvem!</t>
         </is>
       </c>
     </row>
@@ -984,9 +959,9 @@
           <t>(#self gives a weird stare into thin air)</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>(#self olhou curiosamente para o ar).</t>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>(#self encara o vazio com um olhar esquisito)</t>
         </is>
       </c>
     </row>
@@ -1018,9 +993,9 @@
           <t>I yield! You are good.</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Fui derrotado! Você venceu.</t>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>Desisto! Você é bom.</t>
         </is>
       </c>
     </row>
@@ -1038,9 +1013,9 @@
           <t>Accept this as a commemoration of your victory.</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Leve isso como uma lembrança de sua vitória.</t>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>Aceite isto como comemoração da sua vitória.</t>
         </is>
       </c>
     </row>
@@ -1079,9 +1054,9 @@
           <t>That's it, weakling.</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Isso é tudo, fracote.</t>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>É isso, franguinho.</t>
         </is>
       </c>
     </row>
@@ -1120,9 +1095,9 @@
           <t>I didn't expect you to return alive! Go ahead, claim your promised reward.</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Não achei que você voltaria vivo! Agora, receba sua recompensa prometida.</t>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Não esperava que voltasse vivo! Vá em frente, reivindique a recompensa prometida.</t>
         </is>
       </c>
     </row>
@@ -1154,9 +1129,9 @@
           <t>I knew the job was too much for you. How disappointing.</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Parece que a tarefa era muito difícil para você. É uma pena.</t>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>Sabia que o trabalho era demais para você. Que decepção.</t>
         </is>
       </c>
     </row>
@@ -1188,9 +1163,9 @@
           <t xml:space="preserve">Escort me safely to my destination. </t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Me leve em segurança até meu destino.</t>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escolte-me em segurança até meu destino. </t>
         </is>
       </c>
     </row>
@@ -1222,9 +1197,9 @@
           <t>(#self is too pumped up at the party.)</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>(#self está empolgado com a festa).</t>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>(#self está bombando demais na festa.)</t>
         </is>
       </c>
     </row>
@@ -1256,9 +1231,9 @@
           <t>(#self raises a toast to the two of you!)</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>(#self faz um brinde aos dois!)</t>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>(#self brinda aos dois de vocês!)</t>
         </is>
       </c>
     </row>
@@ -1290,9 +1265,9 @@
           <t>(#self smiles at you happily.)</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>(#self sorri feliz para você.)</t>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>(#self sorri para você, feliz.)</t>
         </is>
       </c>
     </row>
@@ -1324,9 +1299,9 @@
           <t>(Pouting in a huff.)</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>(Fazendo beicinho, emburrado.)</t>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>(Faz bico, bufando.)</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1333,7 @@
           <t>...My love. (blushing)</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K117" s="6" t="inlineStr">
         <is>
           <t>...Meu amor. (corando)</t>
         </is>
@@ -1392,9 +1367,9 @@
           <t>Give me #1, or your life is forfeit!</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Se valoriza sua vida, entregue #1 sem resistência!</t>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>Me dê #1, ou sua vida está acabada!</t>
         </is>
       </c>
     </row>
@@ -1425,9 +1400,9 @@
           <t>Try me.</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Tente.</t>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>Tenta.</t>
         </is>
       </c>
     </row>
@@ -1455,9 +1430,9 @@
           <t>I surrender. (Lose: #2)</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Eu me rendo. (Perde: #2)</t>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>Eu me rendo. (Derrota: #2)</t>
         </is>
       </c>
     </row>
@@ -1512,9 +1487,9 @@
           <t>A wise choice.</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>É uma decisão bastante sábia.</t>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>Escolha sábia.</t>
         </is>
       </c>
     </row>
@@ -1553,9 +1528,9 @@
           <t>I want you to have this.</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Quero que você fique com isso.</t>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>Quero que fique com isto.</t>
         </is>
       </c>
     </row>
@@ -1587,9 +1562,9 @@
           <t>I made this... care to try?</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Fiz isso... quer experimentar?</t>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>Fiz isto... quer experimentar?</t>
         </is>
       </c>
     </row>
